--- a/docs/dossiers/dossier-paris-c99746ee.xlsx
+++ b/docs/dossiers/dossier-paris-c99746ee.xlsx
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>60 000 € 1 666,67 €/m² Vente Tabac/Loto/presse 36 m² 36 m² Lorette-Martyrs, Paris 9ème arrondissement (75009) Voir l'annonce</t>
+          <t>1 nouvelle annonce dans votre zone personnalisée : Paris Votre recherche : Vente &gt; Boutique, Local commercial &gt; Paris &gt; Maximum 300,000 € 62 000 € Hôtel / Restaurant 33 m² Trudaine-Maubeuge, Paris 9ème arrondissement (75009) KAPITOL IMMOBILIER Voir l'annonce Se désinscrire | Nous contacter Cet e-mail vous a été envoyé sur georgesdurand75+lesmurs@gmail.com parce que vous avez souscrit à une alerte sur SeLoger bureaux et commerces. SeLoger bureaux et commerces / Digital Classifieds France · 2-8, rue des Italiens · 75009 Paris Conformément à la loi Informatique et Libertés, vous pouvez accéder aux données vous concernant, les faire rectifier ou demander leur effacement. Vous disposez également d'un droit d'opposition, d'un droit à la portabilité et d'un droit à la limitation du traitement des données qui vous concernent. SeLoger bureaux et commerces • SLBCM-202609-ALI-STANDARD</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-c99746ee.xlsx
+++ b/docs/dossiers/dossier-paris-c99746ee.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-c99746ee.xlsx
+++ b/docs/dossiers/dossier-paris-c99746ee.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-c99746ee.xlsx
+++ b/docs/dossiers/dossier-paris-c99746ee.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
